--- a/jaspr/web/cicada_ig/ValueSet-eval-status.xlsx
+++ b/jaspr/web/cicada_ig/ValueSet-eval-status.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T14:37:07-05:00</t>
+    <t>2026-09-02T22:18:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +82,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Value Set for the status of the result of an evaluation.</t>
+    <t>Combined value set for dose evaluation status, including HL7 THO standard codes (valid, notvalid) and the Cicada extension code (extraneous).</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -96,34 +97,25 @@
     <t>BooleanType[null]</t>
   </si>
   <si>
+    <t>Codes</t>
+  </si>
+  <si>
+    <t>All codes</t>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/immunization-evaluation-dose-status</t>
+  </si>
+  <si>
     <t>Concept</t>
   </si>
   <si>
-    <t>valid</t>
-  </si>
-  <si>
-    <t>Valid</t>
-  </si>
-  <si>
-    <t>not_valid</t>
-  </si>
-  <si>
-    <t>Not Valid</t>
-  </si>
-  <si>
     <t>extraneous</t>
   </si>
   <si>
     <t>Extraneous</t>
-  </si>
-  <si>
-    <t>sub_standard</t>
-  </si>
-  <si>
-    <t>Substandard</t>
-  </si>
-  <si>
-    <t>System URI</t>
   </si>
   <si>
     <t>http://fhirfli.dev/fhir/ig/cicada/CodeSystem/EvalStatus</t>
@@ -388,7 +380,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -399,56 +391,72 @@
       <c r="A1" t="s" s="1">
         <v>27</v>
       </c>
-      <c r="B1" t="s" s="1">
-        <v>21</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
         <v>28</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>29</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>31</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
         <v>32</v>
       </c>
+      <c r="B2" t="s" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>29</v>
+      </c>
       <c r="B4" t="s" s="2">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
         <v>34</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/jaspr/web/cicada_ig/ValueSet-eval-status.xlsx
+++ b/jaspr/web/cicada_ig/ValueSet-eval-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T22:18:14-04:00</t>
+    <t>2026-09-06T20:44:07-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/ValueSet-eval-status.xlsx
+++ b/jaspr/web/cicada_ig/ValueSet-eval-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T20:44:07-04:00</t>
+    <t>2026-09-06T23:13:14-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/ValueSet-eval-status.xlsx
+++ b/jaspr/web/cicada_ig/ValueSet-eval-status.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-06T23:13:14-04:00</t>
+    <t>2026-09-07T18:40:23-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jaspr/web/cicada_ig/ValueSet-eval-status.xlsx
+++ b/jaspr/web/cicada_ig/ValueSet-eval-status.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>Property</t>
   </si>
@@ -55,10 +55,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T18:40:23-04:00</t>
+    <t>2026-09-07T19:28:06-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -311,66 +314,68 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -389,28 +394,28 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -429,34 +434,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/jaspr/web/cicada_ig/ValueSet-eval-status.xlsx
+++ b/jaspr/web/cicada_ig/ValueSet-eval-status.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T19:28:06-04:00</t>
+    <t>2026-09-07T19:51:55-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
